--- a/data/price tracker_swiss_2026 0814_v1.xlsx
+++ b/data/price tracker_swiss_2026 0814_v1.xlsx
@@ -535,11 +535,6 @@
       <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="3" hidden="1">
       <c r="A3" t="inlineStr">
@@ -574,11 +569,6 @@
       <c r="I3" t="n">
         <v>0</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="4" hidden="1">
       <c r="A4" t="inlineStr">
@@ -613,11 +603,6 @@
       <c r="I4" t="n">
         <v>0</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="5" hidden="1">
       <c r="A5" t="inlineStr">
@@ -652,11 +637,6 @@
       <c r="I5" t="n">
         <v>0</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -691,11 +671,6 @@
       <c r="I6" t="n">
         <v>0</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="7" hidden="1">
       <c r="A7" t="inlineStr">
@@ -730,11 +705,6 @@
       <c r="I7" t="n">
         <v>0</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="8" hidden="1">
       <c r="A8" t="inlineStr">
@@ -769,11 +739,6 @@
       <c r="I8" t="n">
         <v>0</v>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="9" hidden="1">
       <c r="A9" t="inlineStr">
@@ -808,11 +773,6 @@
       <c r="I9" t="n">
         <v>0</v>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -847,11 +807,6 @@
       <c r="I10" t="n">
         <v>0</v>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="11" hidden="1">
       <c r="A11" t="inlineStr">
@@ -886,11 +841,6 @@
       <c r="I11" t="n">
         <v>0</v>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="12" customFormat="1" s="1">
       <c r="A12" t="inlineStr">
@@ -925,11 +875,6 @@
       <c r="I12" t="n">
         <v>0</v>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="13" hidden="1">
       <c r="A13" t="inlineStr">
@@ -964,11 +909,6 @@
       <c r="I13" t="n">
         <v>0</v>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1003,11 +943,6 @@
       <c r="I14" t="n">
         <v>0</v>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1042,11 +977,6 @@
       <c r="I15" t="n">
         <v>0</v>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="16" hidden="1">
       <c r="A16" t="inlineStr">
@@ -1081,11 +1011,6 @@
       <c r="I16" t="n">
         <v>0</v>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="17" hidden="1">
       <c r="A17" t="inlineStr">
@@ -1120,11 +1045,6 @@
       <c r="I17" t="n">
         <v>0</v>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="18" hidden="1">
       <c r="A18" t="inlineStr">
@@ -1159,11 +1079,6 @@
       <c r="I18" t="n">
         <v>0</v>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="19" hidden="1">
       <c r="A19" t="inlineStr">
@@ -1198,11 +1113,6 @@
       <c r="I19" t="n">
         <v>0</v>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="20" hidden="1">
       <c r="A20" t="inlineStr">
@@ -1237,11 +1147,6 @@
       <c r="I20" t="n">
         <v>0</v>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1276,11 +1181,6 @@
       <c r="I21" t="n">
         <v>0</v>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="22" hidden="1">
       <c r="A22" t="inlineStr">
@@ -1315,11 +1215,6 @@
       <c r="I22" t="n">
         <v>0</v>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="23" hidden="1">
       <c r="A23" t="inlineStr">
@@ -1354,11 +1249,6 @@
       <c r="I23" t="n">
         <v>0</v>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="24" hidden="1">
       <c r="A24" t="inlineStr">
@@ -1393,11 +1283,6 @@
       <c r="I24" t="n">
         <v>0</v>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="25" hidden="1">
       <c r="A25" t="inlineStr">
@@ -1432,11 +1317,6 @@
       <c r="I25" t="n">
         <v>0</v>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="26" hidden="1">
       <c r="A26" t="inlineStr">
@@ -1471,11 +1351,6 @@
       <c r="I26" t="n">
         <v>0</v>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="27" hidden="1">
       <c r="A27" t="inlineStr">
@@ -1510,11 +1385,6 @@
       <c r="I27" t="n">
         <v>0</v>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="28" hidden="1">
       <c r="A28" t="inlineStr">
@@ -1549,11 +1419,6 @@
       <c r="I28" t="n">
         <v>0</v>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="29" hidden="1">
       <c r="A29" t="inlineStr">
@@ -1588,11 +1453,6 @@
       <c r="I29" t="n">
         <v>0</v>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="30" hidden="1">
       <c r="A30" t="inlineStr">
@@ -1627,11 +1487,6 @@
       <c r="I30" t="n">
         <v>0</v>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="31" hidden="1">
       <c r="A31" t="inlineStr">
@@ -1666,11 +1521,6 @@
       <c r="I31" t="n">
         <v>0</v>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="32" hidden="1">
       <c r="A32" t="inlineStr">
@@ -1705,11 +1555,6 @@
       <c r="I32" t="n">
         <v>0</v>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="33" hidden="1">
       <c r="A33" t="inlineStr">
@@ -1744,11 +1589,6 @@
       <c r="I33" t="n">
         <v>0</v>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="34" hidden="1">
       <c r="A34" t="inlineStr">
@@ -1783,11 +1623,6 @@
       <c r="I34" t="n">
         <v>0</v>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="35" hidden="1">
       <c r="A35" t="inlineStr">
@@ -1822,11 +1657,6 @@
       <c r="I35" t="n">
         <v>0</v>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="36" hidden="1">
       <c r="A36" t="inlineStr">
@@ -1861,11 +1691,6 @@
       <c r="I36" t="n">
         <v>0</v>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="37" hidden="1">
       <c r="A37" t="inlineStr">
@@ -1900,11 +1725,6 @@
       <c r="I37" t="n">
         <v>0</v>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="38" hidden="1">
       <c r="A38" t="inlineStr">
@@ -1939,11 +1759,6 @@
       <c r="I38" t="n">
         <v>0</v>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="39" hidden="1">
       <c r="A39" t="inlineStr">
@@ -1978,11 +1793,6 @@
       <c r="I39" t="n">
         <v>0</v>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="40" hidden="1">
       <c r="A40" t="inlineStr">
@@ -2017,11 +1827,6 @@
       <c r="I40" t="n">
         <v>0</v>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="41" hidden="1">
       <c r="A41" t="inlineStr">
@@ -2056,11 +1861,6 @@
       <c r="I41" t="n">
         <v>0</v>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="42" hidden="1">
       <c r="A42" t="inlineStr">
@@ -2095,11 +1895,6 @@
       <c r="I42" t="n">
         <v>0</v>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="43" hidden="1">
       <c r="A43" t="inlineStr">
@@ -2134,11 +1929,6 @@
       <c r="I43" t="n">
         <v>0</v>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="44" hidden="1">
       <c r="A44" t="inlineStr">
@@ -2173,11 +1963,6 @@
       <c r="I44" t="n">
         <v>0</v>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="45" hidden="1">
       <c r="A45" t="inlineStr">
@@ -2212,11 +1997,6 @@
       <c r="I45" t="n">
         <v>0</v>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="46" hidden="1">
       <c r="A46" t="inlineStr">
@@ -2251,11 +2031,6 @@
       <c r="I46" t="n">
         <v>0</v>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="47" hidden="1">
       <c r="A47" t="inlineStr">
@@ -2290,11 +2065,6 @@
       <c r="I47" t="n">
         <v>0</v>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="48" hidden="1">
       <c r="A48" t="inlineStr">
@@ -2329,11 +2099,6 @@
       <c r="I48" t="n">
         <v>0</v>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="49" hidden="1">
       <c r="A49" t="inlineStr">
@@ -2368,11 +2133,6 @@
       <c r="I49" t="n">
         <v>0</v>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="50" hidden="1">
       <c r="A50" t="inlineStr">
@@ -2407,11 +2167,6 @@
       <c r="I50" t="n">
         <v>0</v>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="51" hidden="1">
       <c r="A51" t="inlineStr">
@@ -2446,11 +2201,6 @@
       <c r="I51" t="n">
         <v>0</v>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="52" hidden="1">
       <c r="A52" t="inlineStr">
@@ -2485,11 +2235,6 @@
       <c r="I52" t="n">
         <v>0</v>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="53" hidden="1">
       <c r="A53" t="inlineStr">
@@ -2524,11 +2269,6 @@
       <c r="I53" t="n">
         <v>0</v>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="54" hidden="1">
       <c r="A54" t="inlineStr">
@@ -2563,11 +2303,6 @@
       <c r="I54" t="n">
         <v>0</v>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="55" hidden="1">
       <c r="A55" t="inlineStr">
@@ -2602,11 +2337,6 @@
       <c r="I55" t="n">
         <v>0</v>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="56" hidden="1">
       <c r="A56" t="inlineStr">
@@ -2641,11 +2371,6 @@
       <c r="I56" t="n">
         <v>0</v>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="57" hidden="1">
       <c r="A57" t="inlineStr">
@@ -2680,11 +2405,6 @@
       <c r="I57" t="n">
         <v>0</v>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="58" hidden="1">
       <c r="A58" t="inlineStr">
@@ -2719,11 +2439,6 @@
       <c r="I58" t="n">
         <v>0</v>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="59" hidden="1">
       <c r="A59" t="inlineStr">
@@ -2758,11 +2473,6 @@
       <c r="I59" t="n">
         <v>0</v>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="60" hidden="1">
       <c r="A60" t="inlineStr">
@@ -2797,11 +2507,6 @@
       <c r="I60" t="n">
         <v>0</v>
       </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="61" hidden="1">
       <c r="A61" t="inlineStr">
@@ -2836,11 +2541,6 @@
       <c r="I61" t="n">
         <v>0</v>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="62" hidden="1">
       <c r="A62" t="inlineStr">
@@ -2875,11 +2575,6 @@
       <c r="I62" t="n">
         <v>0</v>
       </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="63" hidden="1">
       <c r="A63" t="inlineStr">
@@ -2914,11 +2609,6 @@
       <c r="I63" t="n">
         <v>0</v>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="64" hidden="1">
       <c r="A64" t="inlineStr">
@@ -2953,11 +2643,6 @@
       <c r="I64" t="n">
         <v>0</v>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="65" hidden="1">
       <c r="A65" t="inlineStr">
@@ -2992,11 +2677,6 @@
       <c r="I65" t="n">
         <v>0</v>
       </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="66" hidden="1">
       <c r="A66" t="inlineStr">
@@ -3031,11 +2711,6 @@
       <c r="I66" t="n">
         <v>0</v>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="67" hidden="1">
       <c r="A67" t="inlineStr">
@@ -3070,11 +2745,6 @@
       <c r="I67" t="n">
         <v>0</v>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="68" hidden="1">
       <c r="A68" t="inlineStr">
@@ -3109,11 +2779,6 @@
       <c r="I68" t="n">
         <v>0</v>
       </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="69" hidden="1">
       <c r="A69" t="inlineStr">
@@ -3148,11 +2813,6 @@
       <c r="I69" t="n">
         <v>0</v>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="70" hidden="1">
       <c r="A70" t="inlineStr">
@@ -3187,11 +2847,6 @@
       <c r="I70" t="n">
         <v>0</v>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="71" hidden="1">
       <c r="A71" t="inlineStr">
@@ -3226,11 +2881,6 @@
       <c r="I71" t="n">
         <v>0</v>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="72" hidden="1">
       <c r="A72" t="inlineStr">
@@ -3265,11 +2915,6 @@
       <c r="I72" t="n">
         <v>0</v>
       </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="73" hidden="1">
       <c r="A73" t="inlineStr">
@@ -3304,11 +2949,6 @@
       <c r="I73" t="n">
         <v>0</v>
       </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="74" hidden="1">
       <c r="A74" t="inlineStr">
@@ -3343,11 +2983,6 @@
       <c r="I74" t="n">
         <v>0</v>
       </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3382,11 +3017,6 @@
       <c r="I75" t="n">
         <v>0</v>
       </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3421,11 +3051,6 @@
       <c r="I76" t="n">
         <v>0</v>
       </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3459,11 +3084,6 @@
       </c>
       <c r="I77" t="n">
         <v>0</v>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -3589,11 +3209,6 @@
       <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="3" hidden="1">
       <c r="A3" t="inlineStr">
@@ -3628,11 +3243,6 @@
       <c r="I3" t="n">
         <v>0</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="4" hidden="1">
       <c r="A4" t="inlineStr">
@@ -3667,11 +3277,6 @@
       <c r="I4" t="n">
         <v>0</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="5" hidden="1">
       <c r="A5" t="inlineStr">
@@ -3706,11 +3311,6 @@
       <c r="I5" t="n">
         <v>0</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="6" hidden="1">
       <c r="A6" t="inlineStr">
@@ -3745,11 +3345,6 @@
       <c r="I6" t="n">
         <v>0</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="7" hidden="1">
       <c r="A7" t="inlineStr">
@@ -3784,11 +3379,6 @@
       <c r="I7" t="n">
         <v>0</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="8" hidden="1">
       <c r="A8" t="inlineStr">
@@ -3823,11 +3413,6 @@
       <c r="I8" t="n">
         <v>0</v>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3862,11 +3447,6 @@
       <c r="I9" t="n">
         <v>0</v>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="10" hidden="1">
       <c r="A10" t="inlineStr">
@@ -3901,11 +3481,6 @@
       <c r="I10" t="n">
         <v>0</v>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="11" hidden="1">
       <c r="A11" t="inlineStr">
@@ -3940,11 +3515,6 @@
       <c r="I11" t="n">
         <v>0</v>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="12" hidden="1">
       <c r="A12" t="inlineStr">
@@ -3981,7 +3551,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -4018,11 +3588,6 @@
       <c r="I13" t="n">
         <v>0</v>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="14" hidden="1">
       <c r="A14" t="inlineStr">
@@ -4057,11 +3622,6 @@
       <c r="I14" t="n">
         <v>0</v>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="15" hidden="1">
       <c r="A15" t="inlineStr">
@@ -4098,7 +3658,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -4135,11 +3695,6 @@
       <c r="I16" t="n">
         <v>0</v>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="17" hidden="1">
       <c r="A17" t="inlineStr">
@@ -4174,11 +3729,6 @@
       <c r="I17" t="n">
         <v>0</v>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="18" hidden="1">
       <c r="A18" t="inlineStr">
@@ -4213,11 +3763,6 @@
       <c r="I18" t="n">
         <v>0</v>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="19" hidden="1">
       <c r="A19" t="inlineStr">
@@ -4252,11 +3797,6 @@
       <c r="I19" t="n">
         <v>0</v>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="20" hidden="1">
       <c r="A20" t="inlineStr">
@@ -4291,11 +3831,6 @@
       <c r="I20" t="n">
         <v>0</v>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="21" hidden="1">
       <c r="A21" t="inlineStr">
@@ -4330,11 +3865,6 @@
       <c r="I21" t="n">
         <v>0</v>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="22" hidden="1">
       <c r="A22" t="inlineStr">
@@ -4371,7 +3901,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -4408,11 +3938,6 @@
       <c r="I23" t="n">
         <v>0</v>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="24" hidden="1">
       <c r="A24" t="inlineStr">
@@ -4447,11 +3972,6 @@
       <c r="I24" t="n">
         <v>0</v>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="25" hidden="1">
       <c r="A25" t="inlineStr">
@@ -4486,11 +4006,6 @@
       <c r="I25" t="n">
         <v>0</v>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4527,7 +4042,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -4564,11 +4079,6 @@
       <c r="I27" t="n">
         <v>0</v>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="28" hidden="1">
       <c r="A28" t="inlineStr">
@@ -4603,11 +4113,6 @@
       <c r="I28" t="n">
         <v>0</v>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="29" hidden="1">
       <c r="A29" t="inlineStr">
@@ -4642,11 +4147,6 @@
       <c r="I29" t="n">
         <v>0</v>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="30" hidden="1">
       <c r="A30" t="inlineStr">
@@ -4683,7 +4183,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -4722,7 +4222,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -4759,11 +4259,6 @@
       <c r="I32" t="n">
         <v>0</v>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4798,11 +4293,6 @@
       <c r="I33" t="n">
         <v>0</v>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="34" hidden="1">
       <c r="A34" t="inlineStr">
@@ -4837,11 +4327,6 @@
       <c r="I34" t="n">
         <v>0</v>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="35" hidden="1">
       <c r="A35" t="inlineStr">
@@ -4876,11 +4361,6 @@
       <c r="I35" t="n">
         <v>0</v>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="36" hidden="1">
       <c r="A36" t="inlineStr">
@@ -4915,11 +4395,6 @@
       <c r="I36" t="n">
         <v>0</v>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="37" hidden="1">
       <c r="A37" t="inlineStr">
@@ -4954,11 +4429,6 @@
       <c r="I37" t="n">
         <v>0</v>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4993,11 +4463,6 @@
       <c r="I38" t="n">
         <v>0</v>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="39" hidden="1">
       <c r="A39" t="inlineStr">
@@ -5034,7 +4499,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -5073,7 +4538,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -5112,7 +4577,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -5151,7 +4616,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -5188,11 +4653,6 @@
       <c r="I43" t="n">
         <v>0</v>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="44" hidden="1">
       <c r="A44" t="inlineStr">
@@ -5227,11 +4687,6 @@
       <c r="I44" t="n">
         <v>0</v>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="45" hidden="1">
       <c r="A45" t="inlineStr">
@@ -5266,11 +4721,6 @@
       <c r="I45" t="n">
         <v>0</v>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="46" hidden="1">
       <c r="A46" t="inlineStr">
@@ -5307,7 +4757,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -5346,7 +4796,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -5383,11 +4833,6 @@
       <c r="I48" t="n">
         <v>0</v>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5422,11 +4867,6 @@
       <c r="I49" t="n">
         <v>0</v>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5461,11 +4901,6 @@
       <c r="I50" t="n">
         <v>0</v>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5502,7 +4937,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -5539,11 +4974,6 @@
       <c r="I52" t="n">
         <v>0</v>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5578,11 +5008,6 @@
       <c r="I53" t="n">
         <v>0</v>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5617,11 +5042,6 @@
       <c r="I54" t="n">
         <v>0</v>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5656,11 +5076,6 @@
       <c r="I55" t="n">
         <v>0</v>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5695,11 +5110,6 @@
       <c r="I56" t="n">
         <v>0</v>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5733,11 +5143,6 @@
       </c>
       <c r="I57" t="n">
         <v>0</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -5860,11 +5265,6 @@
       <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5899,11 +5299,6 @@
       <c r="I3" t="n">
         <v>0</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5938,11 +5333,6 @@
       <c r="I4" t="n">
         <v>0</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5977,11 +5367,6 @@
       <c r="I5" t="n">
         <v>0</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6016,11 +5401,6 @@
       <c r="I6" t="n">
         <v>0</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6055,11 +5435,6 @@
       <c r="I7" t="n">
         <v>0</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6094,11 +5469,6 @@
       <c r="I8" t="n">
         <v>0</v>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6133,11 +5503,6 @@
       <c r="I9" t="n">
         <v>0</v>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6172,11 +5537,6 @@
       <c r="I10" t="n">
         <v>0</v>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6211,11 +5571,6 @@
       <c r="I11" t="n">
         <v>0</v>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6250,11 +5605,6 @@
       <c r="I12" t="n">
         <v>0</v>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6289,11 +5639,6 @@
       <c r="I13" t="n">
         <v>0</v>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6328,11 +5673,6 @@
       <c r="I14" t="n">
         <v>0</v>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6367,11 +5707,6 @@
       <c r="I15" t="n">
         <v>0</v>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6406,11 +5741,6 @@
       <c r="I16" t="n">
         <v>0</v>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6445,11 +5775,6 @@
       <c r="I17" t="n">
         <v>0</v>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6484,11 +5809,6 @@
       <c r="I18" t="n">
         <v>0</v>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6523,11 +5843,6 @@
       <c r="I19" t="n">
         <v>0</v>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6562,11 +5877,6 @@
       <c r="I20" t="n">
         <v>0</v>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6601,11 +5911,6 @@
       <c r="I21" t="n">
         <v>0</v>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6640,11 +5945,6 @@
       <c r="I22" t="n">
         <v>0</v>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6679,11 +5979,6 @@
       <c r="I23" t="n">
         <v>0</v>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6718,11 +6013,6 @@
       <c r="I24" t="n">
         <v>0</v>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6757,11 +6047,6 @@
       <c r="I25" t="n">
         <v>0</v>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6796,11 +6081,6 @@
       <c r="I26" t="n">
         <v>0</v>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6835,11 +6115,6 @@
       <c r="I27" t="n">
         <v>0</v>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6874,11 +6149,6 @@
       <c r="I28" t="n">
         <v>0</v>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6913,11 +6183,6 @@
       <c r="I29" t="n">
         <v>0</v>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6952,11 +6217,6 @@
       <c r="I30" t="n">
         <v>0</v>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6991,11 +6251,6 @@
       <c r="I31" t="n">
         <v>0</v>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -7030,11 +6285,6 @@
       <c r="I32" t="n">
         <v>0</v>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7069,11 +6319,6 @@
       <c r="I33" t="n">
         <v>0</v>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7108,11 +6353,6 @@
       <c r="I34" t="n">
         <v>0</v>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -7147,11 +6387,6 @@
       <c r="I35" t="n">
         <v>0</v>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -7186,11 +6421,6 @@
       <c r="I36" t="n">
         <v>0</v>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -7225,11 +6455,6 @@
       <c r="I37" t="n">
         <v>0</v>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -7264,11 +6489,6 @@
       <c r="I38" t="n">
         <v>0</v>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -7303,11 +6523,6 @@
       <c r="I39" t="n">
         <v>0</v>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -7342,11 +6557,6 @@
       <c r="I40" t="n">
         <v>0</v>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -7381,11 +6591,6 @@
       <c r="I41" t="n">
         <v>0</v>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -7420,11 +6625,6 @@
       <c r="I42" t="n">
         <v>0</v>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -7459,11 +6659,6 @@
       <c r="I43" t="n">
         <v>0</v>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -7498,11 +6693,6 @@
       <c r="I44" t="n">
         <v>0</v>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -7537,11 +6727,6 @@
       <c r="I45" t="n">
         <v>0</v>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -7576,11 +6761,6 @@
       <c r="I46" t="n">
         <v>0</v>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -7615,11 +6795,6 @@
       <c r="I47" t="n">
         <v>0</v>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7654,11 +6829,6 @@
       <c r="I48" t="n">
         <v>0</v>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -7693,11 +6863,6 @@
       <c r="I49" t="n">
         <v>0</v>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7732,11 +6897,6 @@
       <c r="I50" t="n">
         <v>0</v>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7771,11 +6931,6 @@
       <c r="I51" t="n">
         <v>0</v>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7810,11 +6965,6 @@
       <c r="I52" t="n">
         <v>0</v>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7849,11 +6999,6 @@
       <c r="I53" t="n">
         <v>0</v>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7888,11 +7033,6 @@
       <c r="I54" t="n">
         <v>0</v>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7927,11 +7067,6 @@
       <c r="I55" t="n">
         <v>0</v>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7966,11 +7101,6 @@
       <c r="I56" t="n">
         <v>0</v>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -8005,11 +7135,6 @@
       <c r="I57" t="n">
         <v>0</v>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -8044,11 +7169,6 @@
       <c r="I58" t="n">
         <v>0</v>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -8083,11 +7203,6 @@
       <c r="I59" t="n">
         <v>0</v>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -8122,11 +7237,6 @@
       <c r="I60" t="n">
         <v>0</v>
       </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -8161,11 +7271,6 @@
       <c r="I61" t="n">
         <v>0</v>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -8200,11 +7305,6 @@
       <c r="I62" t="n">
         <v>0</v>
       </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -8239,11 +7339,6 @@
       <c r="I63" t="n">
         <v>0</v>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8278,11 +7373,6 @@
       <c r="I64" t="n">
         <v>0</v>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -8317,11 +7407,6 @@
       <c r="I65" t="n">
         <v>0</v>
       </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -8356,11 +7441,6 @@
       <c r="I66" t="n">
         <v>0</v>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -8395,11 +7475,6 @@
       <c r="I67" t="n">
         <v>0</v>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8434,11 +7509,6 @@
       <c r="I68" t="n">
         <v>0</v>
       </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8473,11 +7543,6 @@
       <c r="I69" t="n">
         <v>0</v>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -8512,11 +7577,6 @@
       <c r="I70" t="n">
         <v>0</v>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -8551,11 +7611,6 @@
       <c r="I71" t="n">
         <v>0</v>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -8590,11 +7645,6 @@
       <c r="I72" t="n">
         <v>0</v>
       </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -8629,11 +7679,6 @@
       <c r="I73" t="n">
         <v>0</v>
       </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8668,11 +7713,6 @@
       <c r="I74" t="n">
         <v>0</v>
       </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8707,11 +7747,6 @@
       <c r="I75" t="n">
         <v>0</v>
       </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -8746,11 +7781,6 @@
       <c r="I76" t="n">
         <v>0</v>
       </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8785,11 +7815,6 @@
       <c r="I77" t="n">
         <v>0</v>
       </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8824,11 +7849,6 @@
       <c r="I78" t="n">
         <v>0</v>
       </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8863,11 +7883,6 @@
       <c r="I79" t="n">
         <v>0</v>
       </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8902,11 +7917,6 @@
       <c r="I80" t="n">
         <v>0</v>
       </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8941,11 +7951,6 @@
       <c r="I81" t="n">
         <v>0</v>
       </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8979,11 +7984,6 @@
       </c>
       <c r="I82" t="n">
         <v>0</v>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -9096,11 +8096,6 @@
       <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9135,11 +8130,6 @@
       <c r="I3" t="n">
         <v>0</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9174,11 +8164,6 @@
       <c r="I4" t="n">
         <v>0</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9252,11 +8237,6 @@
       <c r="I6" t="n">
         <v>0</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9291,11 +8271,6 @@
       <c r="I7" t="n">
         <v>0</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9330,11 +8305,6 @@
       <c r="I8" t="n">
         <v>0</v>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9408,11 +8378,6 @@
       <c r="I10" t="n">
         <v>0</v>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9447,11 +8412,6 @@
       <c r="I11" t="n">
         <v>0</v>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9486,11 +8446,6 @@
       <c r="I12" t="n">
         <v>0</v>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9603,11 +8558,6 @@
       <c r="I15" t="n">
         <v>0</v>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9681,11 +8631,6 @@
       <c r="I17" t="n">
         <v>0</v>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9798,11 +8743,6 @@
       <c r="I20" t="n">
         <v>0</v>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9837,11 +8777,6 @@
       <c r="I21" t="n">
         <v>0</v>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9876,11 +8811,6 @@
       <c r="I22" t="n">
         <v>0</v>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9915,11 +8845,6 @@
       <c r="I23" t="n">
         <v>0</v>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -10032,11 +8957,6 @@
       <c r="I26" t="n">
         <v>0</v>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -10071,11 +8991,6 @@
       <c r="I27" t="n">
         <v>0</v>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -10149,11 +9064,6 @@
       <c r="I29" t="n">
         <v>0</v>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -10188,11 +9098,6 @@
       <c r="I30" t="n">
         <v>0</v>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -10227,11 +9132,6 @@
       <c r="I31" t="n">
         <v>0</v>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -10266,11 +9166,6 @@
       <c r="I32" t="n">
         <v>0</v>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -10305,11 +9200,6 @@
       <c r="I33" t="n">
         <v>0</v>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -10344,11 +9234,6 @@
       <c r="I34" t="n">
         <v>0</v>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -10383,11 +9268,6 @@
       <c r="I35" t="n">
         <v>0</v>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -10461,11 +9341,6 @@
       <c r="I37" t="n">
         <v>0</v>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -10500,11 +9375,6 @@
       <c r="I38" t="n">
         <v>0</v>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -10539,11 +9409,6 @@
       <c r="I39" t="n">
         <v>0</v>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -10578,11 +9443,6 @@
       <c r="I40" t="n">
         <v>0</v>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -10616,11 +9476,6 @@
       </c>
       <c r="I41" t="n">
         <v>0</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
       </c>
     </row>
     <row r="42">
@@ -10772,11 +9627,6 @@
       <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10811,11 +9661,6 @@
       <c r="I3" t="n">
         <v>0</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10850,11 +9695,6 @@
       <c r="I4" t="n">
         <v>0</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10889,11 +9729,6 @@
       <c r="I5" t="n">
         <v>0</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10928,11 +9763,6 @@
       <c r="I6" t="n">
         <v>0</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10967,11 +9797,6 @@
       <c r="I7" t="n">
         <v>0</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11006,11 +9831,6 @@
       <c r="I8" t="n">
         <v>0</v>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11045,11 +9865,6 @@
       <c r="I9" t="n">
         <v>0</v>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11084,11 +9899,6 @@
       <c r="I10" t="n">
         <v>0</v>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11123,11 +9933,6 @@
       <c r="I11" t="n">
         <v>0</v>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11162,11 +9967,6 @@
       <c r="I12" t="n">
         <v>0</v>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11201,11 +10001,6 @@
       <c r="I13" t="n">
         <v>0</v>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11240,11 +10035,6 @@
       <c r="I14" t="n">
         <v>0</v>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -11279,11 +10069,6 @@
       <c r="I15" t="n">
         <v>0</v>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -11318,11 +10103,6 @@
       <c r="I16" t="n">
         <v>0</v>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -11357,11 +10137,6 @@
       <c r="I17" t="n">
         <v>0</v>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -11396,11 +10171,6 @@
       <c r="I18" t="n">
         <v>0</v>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -11435,11 +10205,6 @@
       <c r="I19" t="n">
         <v>0</v>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -11474,11 +10239,6 @@
       <c r="I20" t="n">
         <v>0</v>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -11513,11 +10273,6 @@
       <c r="I21" t="n">
         <v>0</v>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -11552,11 +10307,6 @@
       <c r="I22" t="n">
         <v>0</v>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -11591,11 +10341,6 @@
       <c r="I23" t="n">
         <v>0</v>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -11630,11 +10375,6 @@
       <c r="I24" t="n">
         <v>0</v>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -11669,11 +10409,6 @@
       <c r="I25" t="n">
         <v>0</v>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -11708,11 +10443,6 @@
       <c r="I26" t="n">
         <v>0</v>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -11747,11 +10477,6 @@
       <c r="I27" t="n">
         <v>0</v>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -11786,11 +10511,6 @@
       <c r="I28" t="n">
         <v>0</v>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -11825,11 +10545,6 @@
       <c r="I29" t="n">
         <v>0</v>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -11864,11 +10579,6 @@
       <c r="I30" t="n">
         <v>0</v>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -11903,11 +10613,6 @@
       <c r="I31" t="n">
         <v>0</v>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -11942,11 +10647,6 @@
       <c r="I32" t="n">
         <v>0</v>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -11981,11 +10681,6 @@
       <c r="I33" t="n">
         <v>0</v>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -12020,11 +10715,6 @@
       <c r="I34" t="n">
         <v>0</v>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -12059,11 +10749,6 @@
       <c r="I35" t="n">
         <v>0</v>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -12098,11 +10783,6 @@
       <c r="I36" t="n">
         <v>0</v>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -12137,11 +10817,6 @@
       <c r="I37" t="n">
         <v>0</v>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -12176,11 +10851,6 @@
       <c r="I38" t="n">
         <v>0</v>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -12215,11 +10885,6 @@
       <c r="I39" t="n">
         <v>0</v>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -12254,11 +10919,6 @@
       <c r="I40" t="n">
         <v>0</v>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -12293,11 +10953,6 @@
       <c r="I41" t="n">
         <v>0</v>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -12332,11 +10987,6 @@
       <c r="I42" t="n">
         <v>0</v>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -12371,11 +11021,6 @@
       <c r="I43" t="n">
         <v>0</v>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -12410,11 +11055,6 @@
       <c r="I44" t="n">
         <v>0</v>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -12449,11 +11089,6 @@
       <c r="I45" t="n">
         <v>0</v>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -12488,11 +11123,6 @@
       <c r="I46" t="n">
         <v>0</v>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -12527,11 +11157,6 @@
       <c r="I47" t="n">
         <v>0</v>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -12566,11 +11191,6 @@
       <c r="I48" t="n">
         <v>0</v>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -12605,11 +11225,6 @@
       <c r="I49" t="n">
         <v>0</v>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -12644,11 +11259,6 @@
       <c r="I50" t="n">
         <v>0</v>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -12683,11 +11293,6 @@
       <c r="I51" t="n">
         <v>0</v>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -12722,11 +11327,6 @@
       <c r="I52" t="n">
         <v>0</v>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -12761,11 +11361,6 @@
       <c r="I53" t="n">
         <v>0</v>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -12800,11 +11395,6 @@
       <c r="I54" t="n">
         <v>0</v>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -12839,11 +11429,6 @@
       <c r="I55" t="n">
         <v>0</v>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -12878,11 +11463,6 @@
       <c r="I56" t="n">
         <v>0</v>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -12917,11 +11497,6 @@
       <c r="I57" t="n">
         <v>0</v>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -12956,11 +11531,6 @@
       <c r="I58" t="n">
         <v>0</v>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -12995,11 +11565,6 @@
       <c r="I59" t="n">
         <v>0</v>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -13034,11 +11599,6 @@
       <c r="I60" t="n">
         <v>0</v>
       </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -13073,11 +11633,6 @@
       <c r="I61" t="n">
         <v>0</v>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -13112,11 +11667,6 @@
       <c r="I62" t="n">
         <v>0</v>
       </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -13151,11 +11701,6 @@
       <c r="I63" t="n">
         <v>0</v>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -13190,11 +11735,6 @@
       <c r="I64" t="n">
         <v>0</v>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -13229,11 +11769,6 @@
       <c r="I65" t="n">
         <v>0</v>
       </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -13268,11 +11803,6 @@
       <c r="I66" t="n">
         <v>0</v>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -13307,11 +11837,6 @@
       <c r="I67" t="n">
         <v>0</v>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -13346,11 +11871,6 @@
       <c r="I68" t="n">
         <v>0</v>
       </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -13385,11 +11905,6 @@
       <c r="I69" t="n">
         <v>0</v>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -13424,11 +11939,6 @@
       <c r="I70" t="n">
         <v>0</v>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -13463,11 +11973,6 @@
       <c r="I71" t="n">
         <v>0</v>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -13502,11 +12007,6 @@
       <c r="I72" t="n">
         <v>0</v>
       </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -13541,11 +12041,6 @@
       <c r="I73" t="n">
         <v>0</v>
       </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -13580,11 +12075,6 @@
       <c r="I74" t="n">
         <v>0</v>
       </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -13619,11 +12109,6 @@
       <c r="I75" t="n">
         <v>0</v>
       </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -13658,11 +12143,6 @@
       <c r="I76" t="n">
         <v>0</v>
       </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -13697,11 +12177,6 @@
       <c r="I77" t="n">
         <v>0</v>
       </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -13736,11 +12211,6 @@
       <c r="I78" t="n">
         <v>0</v>
       </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -13775,11 +12245,6 @@
       <c r="I79" t="n">
         <v>0</v>
       </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -13814,11 +12279,6 @@
       <c r="I80" t="n">
         <v>0</v>
       </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -13853,11 +12313,6 @@
       <c r="I81" t="n">
         <v>0</v>
       </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -13892,11 +12347,6 @@
       <c r="I82" t="n">
         <v>0</v>
       </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -13931,11 +12381,6 @@
       <c r="I83" t="n">
         <v>0</v>
       </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -13970,11 +12415,6 @@
       <c r="I84" t="n">
         <v>0</v>
       </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -14009,11 +12449,6 @@
       <c r="I85" t="n">
         <v>0</v>
       </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -14048,11 +12483,6 @@
       <c r="I86" t="n">
         <v>0</v>
       </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -14087,11 +12517,6 @@
       <c r="I87" t="n">
         <v>0</v>
       </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -14126,11 +12551,6 @@
       <c r="I88" t="n">
         <v>0</v>
       </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -14164,11 +12584,6 @@
       </c>
       <c r="I89" t="n">
         <v>0</v>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -14282,11 +12697,6 @@
       <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14321,11 +12731,6 @@
       <c r="I3" t="n">
         <v>0</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14360,11 +12765,6 @@
       <c r="I4" t="n">
         <v>0</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14399,11 +12799,6 @@
       <c r="I5" t="n">
         <v>0</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14438,11 +12833,6 @@
       <c r="I6" t="n">
         <v>0</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14477,11 +12867,6 @@
       <c r="I7" t="n">
         <v>0</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14516,11 +12901,6 @@
       <c r="I8" t="n">
         <v>0</v>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14555,11 +12935,6 @@
       <c r="I9" t="n">
         <v>0</v>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14594,11 +12969,6 @@
       <c r="I10" t="n">
         <v>0</v>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14633,11 +13003,6 @@
       <c r="I11" t="n">
         <v>0</v>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14672,11 +13037,6 @@
       <c r="I12" t="n">
         <v>0</v>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -14711,11 +13071,6 @@
       <c r="I13" t="n">
         <v>0</v>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -14750,11 +13105,6 @@
       <c r="I14" t="n">
         <v>0</v>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -14789,11 +13139,6 @@
       <c r="I15" t="n">
         <v>0</v>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -14828,11 +13173,6 @@
       <c r="I16" t="n">
         <v>0</v>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -14867,11 +13207,6 @@
       <c r="I17" t="n">
         <v>0</v>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -14908,7 +13243,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -14945,11 +13280,6 @@
       <c r="I19" t="n">
         <v>0</v>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -14984,11 +13314,6 @@
       <c r="I20" t="n">
         <v>0</v>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -15025,7 +13350,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -15062,11 +13387,6 @@
       <c r="I22" t="n">
         <v>0</v>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -15101,11 +13421,6 @@
       <c r="I23" t="n">
         <v>0</v>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -15140,11 +13455,6 @@
       <c r="I24" t="n">
         <v>0</v>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -15181,7 +13491,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -15218,11 +13528,6 @@
       <c r="I26" t="n">
         <v>0</v>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -15259,7 +13564,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -15298,7 +13603,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -15335,11 +13640,6 @@
       <c r="I29" t="n">
         <v>0</v>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -15374,11 +13674,6 @@
       <c r="I30" t="n">
         <v>0</v>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -15413,11 +13708,6 @@
       <c r="I31" t="n">
         <v>0</v>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -15452,11 +13742,6 @@
       <c r="I32" t="n">
         <v>0</v>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -15491,11 +13776,6 @@
       <c r="I33" t="n">
         <v>0</v>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -15530,11 +13810,6 @@
       <c r="I34" t="n">
         <v>0</v>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -15569,11 +13844,6 @@
       <c r="I35" t="n">
         <v>0</v>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -15608,11 +13878,6 @@
       <c r="I36" t="n">
         <v>0</v>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -15647,11 +13912,6 @@
       <c r="I37" t="n">
         <v>0</v>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -15686,11 +13946,6 @@
       <c r="I38" t="n">
         <v>0</v>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -15725,11 +13980,6 @@
       <c r="I39" t="n">
         <v>0</v>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -15764,11 +14014,6 @@
       <c r="I40" t="n">
         <v>0</v>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -15803,11 +14048,6 @@
       <c r="I41" t="n">
         <v>0</v>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -15842,11 +14082,6 @@
       <c r="I42" t="n">
         <v>0</v>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -15881,11 +14116,6 @@
       <c r="I43" t="n">
         <v>0</v>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -15920,11 +14150,6 @@
       <c r="I44" t="n">
         <v>0</v>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -15959,11 +14184,6 @@
       <c r="I45" t="n">
         <v>0</v>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -15998,11 +14218,6 @@
       <c r="I46" t="n">
         <v>0</v>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -16037,11 +14252,6 @@
       <c r="I47" t="n">
         <v>0</v>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -16078,7 +14288,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -16115,11 +14325,6 @@
       <c r="I49" t="n">
         <v>0</v>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -16154,11 +14359,6 @@
       <c r="I50" t="n">
         <v>0</v>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -16193,11 +14393,6 @@
       <c r="I51" t="n">
         <v>0</v>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -16232,11 +14427,6 @@
       <c r="I52" t="n">
         <v>0</v>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -16271,11 +14461,6 @@
       <c r="I53" t="n">
         <v>0</v>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -16310,11 +14495,6 @@
       <c r="I54" t="n">
         <v>0</v>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -16349,11 +14529,6 @@
       <c r="I55" t="n">
         <v>0</v>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -16390,7 +14565,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -16427,11 +14602,6 @@
       <c r="I57" t="n">
         <v>0</v>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -16466,11 +14636,6 @@
       <c r="I58" t="n">
         <v>0</v>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -16507,7 +14672,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -16544,11 +14709,6 @@
       <c r="I60" t="n">
         <v>0</v>
       </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -16583,11 +14743,6 @@
       <c r="I61" t="n">
         <v>0</v>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -16622,11 +14777,6 @@
       <c r="I62" t="n">
         <v>0</v>
       </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -16661,11 +14811,6 @@
       <c r="I63" t="n">
         <v>0</v>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -16700,11 +14845,6 @@
       <c r="I64" t="n">
         <v>0</v>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -16739,11 +14879,6 @@
       <c r="I65" t="n">
         <v>0</v>
       </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -16778,11 +14913,6 @@
       <c r="I66" t="n">
         <v>0</v>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -16817,11 +14947,6 @@
       <c r="I67" t="n">
         <v>0</v>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -16856,11 +14981,6 @@
       <c r="I68" t="n">
         <v>0</v>
       </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -16895,11 +15015,6 @@
       <c r="I69" t="n">
         <v>0</v>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -16934,11 +15049,6 @@
       <c r="I70" t="n">
         <v>0</v>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -16973,11 +15083,6 @@
       <c r="I71" t="n">
         <v>0</v>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -17012,11 +15117,6 @@
       <c r="I72" t="n">
         <v>0</v>
       </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -17051,11 +15151,6 @@
       <c r="I73" t="n">
         <v>0</v>
       </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -17090,11 +15185,6 @@
       <c r="I74" t="n">
         <v>0</v>
       </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -17129,11 +15219,6 @@
       <c r="I75" t="n">
         <v>0</v>
       </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -17168,11 +15253,6 @@
       <c r="I76" t="n">
         <v>0</v>
       </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -17207,11 +15287,6 @@
       <c r="I77" t="n">
         <v>0</v>
       </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -17246,11 +15321,6 @@
       <c r="I78" t="n">
         <v>0</v>
       </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -17287,7 +15357,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -17324,11 +15394,6 @@
       <c r="I80" t="n">
         <v>0</v>
       </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -17363,11 +15428,6 @@
       <c r="I81" t="n">
         <v>0</v>
       </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -17402,11 +15462,6 @@
       <c r="I82" t="n">
         <v>0</v>
       </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -17443,7 +15498,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -17480,11 +15535,6 @@
       <c r="I84" t="n">
         <v>0</v>
       </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -17519,11 +15569,6 @@
       <c r="I85" t="n">
         <v>0</v>
       </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -17558,11 +15603,6 @@
       <c r="I86" t="n">
         <v>0</v>
       </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -17597,11 +15637,6 @@
       <c r="I87" t="n">
         <v>0</v>
       </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -17636,11 +15671,6 @@
       <c r="I88" t="n">
         <v>0</v>
       </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -17677,7 +15707,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -17716,7 +15746,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -17753,11 +15783,6 @@
       <c r="I91" t="n">
         <v>0</v>
       </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -17792,11 +15817,6 @@
       <c r="I92" t="n">
         <v>0</v>
       </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -17831,11 +15851,6 @@
       <c r="I93" t="n">
         <v>0</v>
       </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -17872,7 +15887,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -17911,7 +15926,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -17948,11 +15963,6 @@
       <c r="I96" t="n">
         <v>0</v>
       </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -17987,11 +15997,6 @@
       <c r="I97" t="n">
         <v>0</v>
       </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -18026,11 +16031,6 @@
       <c r="I98" t="n">
         <v>0</v>
       </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -18065,11 +16065,6 @@
       <c r="I99" t="n">
         <v>0</v>
       </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -18104,11 +16099,6 @@
       <c r="I100" t="n">
         <v>0</v>
       </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -18143,11 +16133,6 @@
       <c r="I101" t="n">
         <v>0</v>
       </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -18184,7 +16169,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -18221,11 +16206,6 @@
       <c r="I103" t="n">
         <v>0</v>
       </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -18260,11 +16240,6 @@
       <c r="I104" t="n">
         <v>0</v>
       </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -18299,11 +16274,6 @@
       <c r="I105" t="n">
         <v>0</v>
       </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -18338,11 +16308,6 @@
       <c r="I106" t="n">
         <v>0</v>
       </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -18377,11 +16342,6 @@
       <c r="I107" t="n">
         <v>0</v>
       </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -18416,11 +16376,6 @@
       <c r="I108" t="n">
         <v>0</v>
       </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -18455,11 +16410,6 @@
       <c r="I109" t="n">
         <v>0</v>
       </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -18494,11 +16444,6 @@
       <c r="I110" t="n">
         <v>0</v>
       </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -18533,11 +16478,6 @@
       <c r="I111" t="n">
         <v>0</v>
       </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -18572,11 +16512,6 @@
       <c r="I112" t="n">
         <v>0</v>
       </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -18611,11 +16546,6 @@
       <c r="I113" t="n">
         <v>0</v>
       </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -18649,11 +16579,6 @@
       </c>
       <c r="I114" t="n">
         <v>0</v>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
       </c>
     </row>
   </sheetData>
